--- a/Testcases/all_login_test_cases_COMPLETE.xlsx
+++ b/Testcases/all_login_test_cases_COMPLETE.xlsx
@@ -7,7 +7,7 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Test Cases" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Login Test Cases" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -28,7 +28,7 @@
     <font>
       <b val="1"/>
       <color rgb="00FFFFFF"/>
-      <sz val="12"/>
+      <sz val="11"/>
     </font>
   </fonts>
   <fills count="3">
@@ -430,39 +430,40 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G30"/>
+  <dimension ref="A1:H30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="30" customWidth="1" min="1" max="1"/>
-    <col width="40" customWidth="1" min="2" max="2"/>
-    <col width="60" customWidth="1" min="3" max="3"/>
-    <col width="70" customWidth="1" min="4" max="4"/>
-    <col width="30" customWidth="1" min="5" max="5"/>
-    <col width="30" customWidth="1" min="6" max="6"/>
-    <col width="15" customWidth="1" min="7" max="7"/>
+    <col width="4" customWidth="1" min="1" max="1"/>
+    <col width="45" customWidth="1" min="2" max="2"/>
+    <col width="22" customWidth="1" min="3" max="3"/>
+    <col width="50" customWidth="1" min="4" max="4"/>
+    <col width="55" customWidth="1" min="5" max="5"/>
+    <col width="12" customWidth="1" min="6" max="6"/>
+    <col width="10" customWidth="1" min="7" max="7"/>
+    <col width="18" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Test Case Name</t>
+          <t>#</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
+          <t>Test ID</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Category</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
           <t>Description</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>Test Steps</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>SQL Queries</t>
-        </is>
-      </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
           <t>Expected Result</t>
@@ -475,1097 +476,827 @@
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>Layers</t>
+          <t>Status</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>Last Run</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="2" t="inlineStr">
+      <c r="A2" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
         <is>
           <t>test_valid_login_redirects_to_dashboard</t>
         </is>
       </c>
-      <c r="B2" s="2" t="inlineStr">
+      <c r="C2" s="2" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
         <is>
           <t>User logs in with valid credentials and is redirected to dashboard</t>
         </is>
       </c>
-      <c r="C2" s="2" t="inlineStr">
-        <is>
-          <t>1. [UI] Verify text appears: User logs in with valid credentials and is redirected to dashboard</t>
-        </is>
-      </c>
-      <c r="D2" s="2" t="inlineStr">
-        <is>
-          <t>1. [verify_user_exists_and_active] (Variables: email)
-   SQL: SELECT is_active FROM auth_user WHERE email = '{email}' LIMIT 1
-   Expected: auth_user.is_active = 1 for the logged-in user
-2. [verify_last_login_updated] (Variables: email)
-   SQL: SELECT last_login FROM auth_user WHERE email = '{email}' LIMIT 1
-   Expected: auth_user.last_login is not null after successful login
-3. [verify_session_exists]
-   SQL: SELECT COUNT(*) FROM django_session WHERE expire_date &gt; NOW()
-   Expected: At least 1 active session exists in django_session</t>
-        </is>
-      </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>User logs in with valid credentials and is redirected to dashboard</t>
+          <t>User is redirected to dashboard; URL contains trinitylifesciences.com</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr"/>
-      <c r="G2" s="2" t="inlineStr">
-        <is>
-          <t>UI</t>
-        </is>
-      </c>
+      <c r="G2" s="2" t="inlineStr"/>
+      <c r="H2" s="2" t="inlineStr"/>
     </row>
     <row r="3">
-      <c r="A3" s="2" t="inlineStr">
+      <c r="A3" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
         <is>
           <t>test_valid_login_email_case_insensitive</t>
         </is>
       </c>
-      <c r="B3" s="2" t="inlineStr">
+      <c r="C3" s="2" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="D3" s="2" t="inlineStr">
         <is>
           <t>Microsoft SSO accepts email regardless of letter case (UPN is case-insensitive)</t>
         </is>
       </c>
-      <c r="C3" s="2" t="inlineStr">
-        <is>
-          <t>1. [UI] Verify text appears: Microsoft SSO accepts email regardless of letter case (UPN is case-insensitive)</t>
-        </is>
-      </c>
-      <c r="D3" s="2" t="inlineStr">
-        <is>
-          <t>1. [verify_user_exists_and_active] (Variables: email)
-   SQL: SELECT is_active FROM auth_user WHERE email = '{email}' LIMIT 1
-   Expected: auth_user.is_active = 1 for the logged-in user
-2. [verify_last_login_updated] (Variables: email)
-   SQL: SELECT last_login FROM auth_user WHERE email = '{email}' LIMIT 1
-   Expected: auth_user.last_login is not null after successful login
-3. [verify_session_exists]
-   SQL: SELECT COUNT(*) FROM django_session WHERE expire_date &gt; NOW()
-   Expected: At least 1 active session exists in django_session</t>
-        </is>
-      </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>Microsoft SSO accepts email regardless of letter case (UPN is case-insensitive)</t>
+          <t>SSO accepts uppercase email and advances to password step</t>
         </is>
       </c>
       <c r="F3" s="2" t="inlineStr"/>
-      <c r="G3" s="2" t="inlineStr">
-        <is>
-          <t>UI</t>
-        </is>
-      </c>
+      <c r="G3" s="2" t="inlineStr"/>
+      <c r="H3" s="2" t="inlineStr"/>
     </row>
     <row r="4">
-      <c r="A4" s="2" t="inlineStr">
+      <c r="A4" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
         <is>
           <t>test_valid_login_email_with_spaces_trimmed</t>
         </is>
       </c>
-      <c r="B4" s="2" t="inlineStr">
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
         <is>
           <t>User enters email with leading/trailing spaces and login succeeds</t>
         </is>
       </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>1. [UI] Verify text appears: User enters email with leading/trailing spaces and login succeeds</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>1. [verify_user_exists_and_active] (Variables: email)
-   SQL: SELECT is_active FROM auth_user WHERE email = '{email}' LIMIT 1
-   Expected: auth_user.is_active = 1 for the logged-in user
-2. [verify_last_login_updated] (Variables: email)
-   SQL: SELECT last_login FROM auth_user WHERE email = '{email}' LIMIT 1
-   Expected: auth_user.last_login is not null after successful login
-3. [verify_session_exists]
-   SQL: SELECT COUNT(*) FROM django_session WHERE expire_date &gt; NOW()
-   Expected: At least 1 active session exists in django_session</t>
-        </is>
-      </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>User enters email with leading/trailing spaces and login succeeds</t>
+          <t>Login succeeds; spaces trimmed from email automatically</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr"/>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>UI</t>
-        </is>
-      </c>
+      <c r="G4" s="2" t="inlineStr"/>
+      <c r="H4" s="2" t="inlineStr"/>
     </row>
     <row r="5">
-      <c r="A5" s="2" t="inlineStr">
+      <c r="A5" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
         <is>
           <t>test_login_page_loads_correctly</t>
         </is>
       </c>
-      <c r="B5" s="2" t="inlineStr">
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
         <is>
           <t>Login page loads with Sign In button visible</t>
         </is>
       </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>1. [UI] Verify text appears: Login page loads with Sign In button visible</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>1. [verify_user_exists_and_active] (Variables: email)
-   SQL: SELECT is_active FROM auth_user WHERE email = '{email}' LIMIT 1
-   Expected: auth_user.is_active = 1 for the logged-in user
-2. [verify_last_login_updated] (Variables: email)
-   SQL: SELECT last_login FROM auth_user WHERE email = '{email}' LIMIT 1
-   Expected: auth_user.last_login is not null after successful login
-3. [verify_session_exists]
-   SQL: SELECT COUNT(*) FROM django_session WHERE expire_date &gt; NOW()
-   Expected: At least 1 active session exists in django_session</t>
-        </is>
-      </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>Login page loads with Sign In button visible</t>
+          <t>Sign In button is visible on the app login page</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr"/>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>UI</t>
-        </is>
-      </c>
+      <c r="G5" s="2" t="inlineStr"/>
+      <c r="H5" s="2" t="inlineStr"/>
     </row>
     <row r="6">
-      <c r="A6" s="2" t="inlineStr">
+      <c r="A6" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
         <is>
           <t>test_forgot_password_link_visible</t>
         </is>
       </c>
-      <c r="B6" s="2" t="inlineStr">
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
         <is>
           <t>Account recovery link is visible on Microsoft SSO password page.
 This tenant shows 'Can't access your account?' (#cantAccessAccount)</t>
         </is>
       </c>
-      <c r="C6" s="2" t="inlineStr">
-        <is>
-          <t>1. [UI] Verify text appears: Account recovery link is visible on Microsoft SSO password page.
-This tenant shows 'Can't access your account?' (#cantAccessAccount)</t>
-        </is>
-      </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>No DB queries defined</t>
-        </is>
-      </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>Account recovery link is visible on Microsoft SSO password page.
-This tenant shows 'Can't access your account?' (#cantAccessAccount)</t>
+          <t>'Can't access your account?' link is visible on SSO password page</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr"/>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>UI</t>
-        </is>
-      </c>
+      <c r="G6" s="2" t="inlineStr"/>
+      <c r="H6" s="2" t="inlineStr"/>
     </row>
     <row r="7">
-      <c r="A7" s="2" t="inlineStr">
+      <c r="A7" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="B7" s="2" t="inlineStr">
         <is>
           <t>test_forgot_password_link_navigates</t>
         </is>
       </c>
-      <c r="B7" s="2" t="inlineStr">
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
         <is>
           <t>'Can't access your account?' link navigates to Microsoft account recovery</t>
         </is>
       </c>
-      <c r="C7" s="2" t="inlineStr">
-        <is>
-          <t>1. [UI] Verify text appears: 'Can't access your account?' link navigates to Microsoft account recovery</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>No DB queries defined</t>
-        </is>
-      </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>'Can't access your account?' link navigates to Microsoft account recovery</t>
+          <t>Clicking recovery link navigates to microsoftonline password reset page</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr"/>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>UI</t>
-        </is>
-      </c>
+      <c r="G7" s="2" t="inlineStr"/>
+      <c r="H7" s="2" t="inlineStr"/>
     </row>
     <row r="8">
-      <c r="A8" s="2" t="inlineStr">
+      <c r="A8" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
         <is>
           <t>test_password_field_is_masked</t>
         </is>
       </c>
-      <c r="B8" s="2" t="inlineStr">
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
         <is>
           <t>Password field on Microsoft SSO is masked (type=password)</t>
         </is>
       </c>
-      <c r="C8" s="2" t="inlineStr">
-        <is>
-          <t>1. [UI] Verify text appears: Password field on Microsoft SSO is masked (type=password)</t>
-        </is>
-      </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>No DB queries defined</t>
-        </is>
-      </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>Password field on Microsoft SSO is masked (type=password)</t>
+          <t>Password input type=password (field is masked)</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr"/>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>UI</t>
-        </is>
-      </c>
+      <c r="G8" s="2" t="inlineStr"/>
+      <c r="H8" s="2" t="inlineStr"/>
     </row>
     <row r="9">
-      <c r="A9" s="2" t="inlineStr">
+      <c r="A9" s="2" t="n">
+        <v>8</v>
+      </c>
+      <c r="B9" s="2" t="inlineStr">
         <is>
           <t>test_login_with_empty_email</t>
         </is>
       </c>
-      <c r="B9" s="2" t="inlineStr">
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>Edge Case</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
         <is>
           <t>User submits empty email on SSO - shows validation error</t>
         </is>
       </c>
-      <c r="C9" s="2" t="inlineStr">
-        <is>
-          <t>1. [UI] Verify text appears: User submits empty email on SSO - shows validation error</t>
-        </is>
-      </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>1. [verify_user_exists_and_active] (Variables: email)
-   SQL: SELECT is_active FROM auth_user WHERE email = '{email}' LIMIT 1
-   Expected: auth_user.is_active = 1 for the logged-in user
-2. [verify_last_login_updated] (Variables: email)
-   SQL: SELECT last_login FROM auth_user WHERE email = '{email}' LIMIT 1
-   Expected: auth_user.last_login is not null after successful login
-3. [verify_session_exists]
-   SQL: SELECT COUNT(*) FROM django_session WHERE expire_date &gt; NOW()
-   Expected: At least 1 active session exists in django_session</t>
-        </is>
-      </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>User submits empty email on SSO - shows validation error</t>
+          <t>User is NOT logged in; SSO shows validation error</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr"/>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>UI</t>
-        </is>
-      </c>
+      <c r="G9" s="2" t="inlineStr"/>
+      <c r="H9" s="2" t="inlineStr"/>
     </row>
     <row r="10">
-      <c r="A10" s="2" t="inlineStr">
+      <c r="A10" s="2" t="n">
+        <v>9</v>
+      </c>
+      <c r="B10" s="2" t="inlineStr">
         <is>
           <t>test_login_with_empty_password</t>
         </is>
       </c>
-      <c r="B10" s="2" t="inlineStr">
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>Edge Case</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
         <is>
           <t>User submits empty password on SSO - shows validation error</t>
         </is>
       </c>
-      <c r="C10" s="2" t="inlineStr">
-        <is>
-          <t>1. [UI] Verify text appears: User submits empty password on SSO - shows validation error</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>1. [verify_user_exists_and_active] (Variables: email)
-   SQL: SELECT is_active FROM auth_user WHERE email = '{email}' LIMIT 1
-   Expected: auth_user.is_active = 1 for the logged-in user
-2. [verify_last_login_updated] (Variables: email)
-   SQL: SELECT last_login FROM auth_user WHERE email = '{email}' LIMIT 1
-   Expected: auth_user.last_login is not null after successful login
-3. [verify_session_exists]
-   SQL: SELECT COUNT(*) FROM django_session WHERE expire_date &gt; NOW()
-   Expected: At least 1 active session exists in django_session</t>
-        </is>
-      </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>User submits empty password on SSO - shows validation error</t>
+          <t>User is NOT logged in; SSO shows validation error</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr"/>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>UI</t>
-        </is>
-      </c>
+      <c r="G10" s="2" t="inlineStr"/>
+      <c r="H10" s="2" t="inlineStr"/>
     </row>
     <row r="11">
-      <c r="A11" s="2" t="inlineStr">
+      <c r="A11" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="B11" s="2" t="inlineStr">
         <is>
           <t>test_login_email_with_plus_sign</t>
         </is>
       </c>
-      <c r="B11" s="2" t="inlineStr">
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>Edge Case</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
         <is>
           <t>Email with + sign is accepted as valid format on SSO page</t>
         </is>
       </c>
-      <c r="C11" s="2" t="inlineStr">
-        <is>
-          <t>1. [UI] Verify text appears: Email with + sign is accepted as valid format on SSO page</t>
-        </is>
-      </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>1. [verify_user_exists_and_active] (Variables: email)
-   SQL: SELECT is_active FROM auth_user WHERE email = '{email}' LIMIT 1
-   Expected: auth_user.is_active = 1 for the logged-in user
-2. [verify_last_login_updated] (Variables: email)
-   SQL: SELECT last_login FROM auth_user WHERE email = '{email}' LIMIT 1
-   Expected: auth_user.last_login is not null after successful login
-3. [verify_session_exists]
-   SQL: SELECT COUNT(*) FROM django_session WHERE expire_date &gt; NOW()
-   Expected: At least 1 active session exists in django_session</t>
-        </is>
-      </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>Email with + sign is accepted as valid format on SSO page</t>
+          <t>SSO stays on microsoftonline; email format with + is accepted</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr"/>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>UI</t>
-        </is>
-      </c>
+      <c r="G11" s="2" t="inlineStr"/>
+      <c r="H11" s="2" t="inlineStr"/>
     </row>
     <row r="12">
-      <c r="A12" s="2" t="inlineStr">
+      <c r="A12" s="2" t="n">
+        <v>11</v>
+      </c>
+      <c r="B12" s="2" t="inlineStr">
         <is>
           <t>test_login_tab_navigation</t>
         </is>
       </c>
-      <c r="B12" s="2" t="inlineStr">
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>Edge Case</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
         <is>
           <t>Tab key navigates from email to next button on SSO</t>
         </is>
       </c>
-      <c r="C12" s="2" t="inlineStr">
-        <is>
-          <t>1. [UI] Verify text appears: Tab key navigates from email to next button on SSO</t>
-        </is>
-      </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>1. [verify_user_exists_and_active] (Variables: email)
-   SQL: SELECT is_active FROM auth_user WHERE email = '{email}' LIMIT 1
-   Expected: auth_user.is_active = 1 for the logged-in user
-2. [verify_last_login_updated] (Variables: email)
-   SQL: SELECT last_login FROM auth_user WHERE email = '{email}' LIMIT 1
-   Expected: auth_user.last_login is not null after successful login
-3. [verify_session_exists]
-   SQL: SELECT COUNT(*) FROM django_session WHERE expire_date &gt; NOW()
-   Expected: At least 1 active session exists in django_session</t>
-        </is>
-      </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>Tab key navigates from email to next button on SSO</t>
+          <t>Focus moves to INPUT, BUTTON, or A element after Tab key</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr"/>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>UI</t>
-        </is>
-      </c>
+      <c r="G12" s="2" t="inlineStr"/>
+      <c r="H12" s="2" t="inlineStr"/>
     </row>
     <row r="13">
-      <c r="A13" s="2" t="inlineStr">
+      <c r="A13" s="2" t="n">
+        <v>12</v>
+      </c>
+      <c r="B13" s="2" t="inlineStr">
         <is>
           <t>test_login_enter_key_submits</t>
         </is>
       </c>
-      <c r="B13" s="2" t="inlineStr">
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>Edge Case</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
         <is>
           <t>Enter key navigates from email to password step on SSO</t>
         </is>
       </c>
-      <c r="C13" s="2" t="inlineStr">
-        <is>
-          <t>1. [UI] Verify text appears: Enter key navigates from email to password step on SSO</t>
-        </is>
-      </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>1. [verify_user_exists_and_active] (Variables: email)
-   SQL: SELECT is_active FROM auth_user WHERE email = '{email}' LIMIT 1
-   Expected: auth_user.is_active = 1 for the logged-in user
-2. [verify_last_login_updated] (Variables: email)
-   SQL: SELECT last_login FROM auth_user WHERE email = '{email}' LIMIT 1
-   Expected: auth_user.last_login is not null after successful login
-3. [verify_session_exists]
-   SQL: SELECT COUNT(*) FROM django_session WHERE expire_date &gt; NOW()
-   Expected: At least 1 active session exists in django_session</t>
-        </is>
-      </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>Enter key navigates from email to password step on SSO</t>
+          <t>Enter key advances to password step on SSO</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr"/>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>UI</t>
-        </is>
-      </c>
+      <c r="G13" s="2" t="inlineStr"/>
+      <c r="H13" s="2" t="inlineStr"/>
     </row>
     <row r="14">
-      <c r="A14" s="2" t="inlineStr">
+      <c r="A14" s="2" t="n">
+        <v>13</v>
+      </c>
+      <c r="B14" s="2" t="inlineStr">
         <is>
           <t>test_login_page_title</t>
         </is>
       </c>
-      <c r="B14" s="2" t="inlineStr">
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>Edge Case</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
         <is>
           <t>Login page has correct title</t>
         </is>
       </c>
-      <c r="C14" s="2" t="inlineStr">
-        <is>
-          <t>1. [UI] Verify text appears: Login page has correct title</t>
-        </is>
-      </c>
-      <c r="D14" s="2" t="inlineStr">
-        <is>
-          <t>1. [verify_user_exists_and_active] (Variables: email)
-   SQL: SELECT is_active FROM auth_user WHERE email = '{email}' LIMIT 1
-   Expected: auth_user.is_active = 1 for the logged-in user
-2. [verify_last_login_updated] (Variables: email)
-   SQL: SELECT last_login FROM auth_user WHERE email = '{email}' LIMIT 1
-   Expected: auth_user.last_login is not null after successful login
-3. [verify_session_exists]
-   SQL: SELECT COUNT(*) FROM django_session WHERE expire_date &gt; NOW()
-   Expected: At least 1 active session exists in django_session</t>
-        </is>
-      </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>Login page has correct title</t>
+          <t>Page title is not empty</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr"/>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>UI</t>
-        </is>
-      </c>
+      <c r="G14" s="2" t="inlineStr"/>
+      <c r="H14" s="2" t="inlineStr"/>
     </row>
     <row r="15">
-      <c r="A15" s="2" t="inlineStr">
+      <c r="A15" s="2" t="n">
+        <v>14</v>
+      </c>
+      <c r="B15" s="2" t="inlineStr">
         <is>
           <t>test_browser_back_after_login</t>
         </is>
       </c>
-      <c r="B15" s="2" t="inlineStr">
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>Edge Case</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
         <is>
           <t>After login, pressing browser back does not expose secured pages</t>
         </is>
       </c>
-      <c r="C15" s="2" t="inlineStr">
-        <is>
-          <t>1. [UI] Verify text appears: After login, pressing browser back does not expose secured pages</t>
-        </is>
-      </c>
-      <c r="D15" s="2" t="inlineStr">
-        <is>
-          <t>1. [verify_user_exists_and_active] (Variables: email)
-   SQL: SELECT is_active FROM auth_user WHERE email = '{email}' LIMIT 1
-   Expected: auth_user.is_active = 1 for the logged-in user
-2. [verify_last_login_updated] (Variables: email)
-   SQL: SELECT last_login FROM auth_user WHERE email = '{email}' LIMIT 1
-   Expected: auth_user.last_login is not null after successful login
-3. [verify_session_exists]
-   SQL: SELECT COUNT(*) FROM django_session WHERE expire_date &gt; NOW()
-   Expected: At least 1 active session exists in django_session</t>
-        </is>
-      </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>After login, pressing browser back does not expose secured pages</t>
+          <t>Browser back stays on trinitylifesciences.com or microsoftonline.com</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr"/>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>UI</t>
-        </is>
-      </c>
+      <c r="G15" s="2" t="inlineStr"/>
+      <c r="H15" s="2" t="inlineStr"/>
     </row>
     <row r="16">
-      <c r="A16" s="2" t="inlineStr">
+      <c r="A16" s="2" t="n">
+        <v>15</v>
+      </c>
+      <c r="B16" s="2" t="inlineStr">
         <is>
           <t>test_invalid_password_shows_error</t>
         </is>
       </c>
-      <c r="B16" s="2" t="inlineStr">
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>Negative / Security</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
         <is>
           <t>User enters wrong password on SSO - error displayed</t>
         </is>
       </c>
-      <c r="C16" s="2" t="inlineStr">
-        <is>
-          <t>1. [UI] Verify text appears: User enters wrong password on SSO - error displayed</t>
-        </is>
-      </c>
-      <c r="D16" s="2" t="inlineStr">
-        <is>
-          <t>No DB queries defined</t>
-        </is>
-      </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>User enters wrong password on SSO - error displayed</t>
+          <t>User is NOT logged in; SSO shows incorrect password error</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr"/>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>UI</t>
-        </is>
-      </c>
+      <c r="G16" s="2" t="inlineStr"/>
+      <c r="H16" s="2" t="inlineStr"/>
     </row>
     <row r="17">
-      <c r="A17" s="2" t="inlineStr">
+      <c r="A17" s="2" t="n">
+        <v>16</v>
+      </c>
+      <c r="B17" s="2" t="inlineStr">
         <is>
           <t>test_invalid_email_shows_error</t>
         </is>
       </c>
-      <c r="B17" s="2" t="inlineStr">
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>Negative / Security</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
         <is>
           <t>User enters unregistered email on SSO - error displayed</t>
         </is>
       </c>
-      <c r="C17" s="2" t="inlineStr">
-        <is>
-          <t>1. [UI] Verify text appears: User enters unregistered email on SSO - error displayed</t>
-        </is>
-      </c>
-      <c r="D17" s="2" t="inlineStr">
-        <is>
-          <t>No DB queries defined</t>
-        </is>
-      </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>User enters unregistered email on SSO - error displayed</t>
+          <t>User is NOT logged in; SSO shows account not found error</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr"/>
-      <c r="G17" s="2" t="inlineStr">
-        <is>
-          <t>UI</t>
-        </is>
-      </c>
+      <c r="G17" s="2" t="inlineStr"/>
+      <c r="H17" s="2" t="inlineStr"/>
     </row>
     <row r="18">
-      <c r="A18" s="2" t="inlineStr">
+      <c r="A18" s="2" t="n">
+        <v>17</v>
+      </c>
+      <c r="B18" s="2" t="inlineStr">
         <is>
           <t>test_invalid_email_format</t>
         </is>
       </c>
-      <c r="B18" s="2" t="inlineStr">
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>Negative / Security</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
         <is>
           <t>User enters invalid email format on SSO - validation error shown</t>
         </is>
       </c>
-      <c r="C18" s="2" t="inlineStr">
-        <is>
-          <t>1. [UI] Verify text appears: User enters invalid email format on SSO - validation error shown</t>
-        </is>
-      </c>
-      <c r="D18" s="2" t="inlineStr">
-        <is>
-          <t>No DB queries defined</t>
-        </is>
-      </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>User enters invalid email format on SSO - validation error shown</t>
+          <t>User is NOT logged in; SSO shows email format error</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr"/>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>UI</t>
-        </is>
-      </c>
+      <c r="G18" s="2" t="inlineStr"/>
+      <c r="H18" s="2" t="inlineStr"/>
     </row>
     <row r="19">
-      <c r="A19" s="2" t="inlineStr">
+      <c r="A19" s="2" t="n">
+        <v>18</v>
+      </c>
+      <c r="B19" s="2" t="inlineStr">
         <is>
           <t>test_sql_injection_in_email</t>
         </is>
       </c>
-      <c r="B19" s="2" t="inlineStr">
+      <c r="C19" s="2" t="inlineStr">
+        <is>
+          <t>Negative / Security</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
         <is>
           <t>SQL injection in email field is blocked by SSO</t>
         </is>
       </c>
-      <c r="C19" s="2" t="inlineStr">
-        <is>
-          <t>1. [UI] Verify text appears: SQL injection in email field is blocked by SSO</t>
-        </is>
-      </c>
-      <c r="D19" s="2" t="inlineStr">
-        <is>
-          <t>No DB queries defined</t>
-        </is>
-      </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>SQL injection in email field is blocked by SSO</t>
+          <t>User is NOT logged in; SQL injection blocked by SSO</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr"/>
-      <c r="G19" s="2" t="inlineStr">
-        <is>
-          <t>UI</t>
-        </is>
-      </c>
+      <c r="G19" s="2" t="inlineStr"/>
+      <c r="H19" s="2" t="inlineStr"/>
     </row>
     <row r="20">
-      <c r="A20" s="2" t="inlineStr">
+      <c r="A20" s="2" t="n">
+        <v>19</v>
+      </c>
+      <c r="B20" s="2" t="inlineStr">
         <is>
           <t>test_sql_injection_in_password</t>
         </is>
       </c>
-      <c r="B20" s="2" t="inlineStr">
+      <c r="C20" s="2" t="inlineStr">
+        <is>
+          <t>Negative / Security</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
         <is>
           <t>SQL injection in password field is blocked by SSO</t>
         </is>
       </c>
-      <c r="C20" s="2" t="inlineStr">
-        <is>
-          <t>1. [UI] Verify text appears: SQL injection in password field is blocked by SSO</t>
-        </is>
-      </c>
-      <c r="D20" s="2" t="inlineStr">
-        <is>
-          <t>No DB queries defined</t>
-        </is>
-      </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>SQL injection in password field is blocked by SSO</t>
+          <t>User is NOT logged in; SQL injection in password blocked</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr"/>
-      <c r="G20" s="2" t="inlineStr">
-        <is>
-          <t>UI</t>
-        </is>
-      </c>
+      <c r="G20" s="2" t="inlineStr"/>
+      <c r="H20" s="2" t="inlineStr"/>
     </row>
     <row r="21">
-      <c r="A21" s="2" t="inlineStr">
+      <c r="A21" s="2" t="n">
+        <v>20</v>
+      </c>
+      <c r="B21" s="2" t="inlineStr">
         <is>
           <t>test_xss_in_email_field</t>
         </is>
       </c>
-      <c r="B21" s="2" t="inlineStr">
+      <c r="C21" s="2" t="inlineStr">
+        <is>
+          <t>Negative / Security</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
         <is>
           <t>XSS script injection in email field is sanitized by SSO</t>
         </is>
       </c>
-      <c r="C21" s="2" t="inlineStr">
-        <is>
-          <t>1. [UI] Verify text appears: XSS script injection in email field is sanitized by SSO</t>
-        </is>
-      </c>
-      <c r="D21" s="2" t="inlineStr">
-        <is>
-          <t>No DB queries defined</t>
-        </is>
-      </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>XSS script injection in email field is sanitized by SSO</t>
+          <t>User is NOT logged in; XSS script not executed</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr"/>
-      <c r="G21" s="2" t="inlineStr">
-        <is>
-          <t>UI</t>
-        </is>
-      </c>
+      <c r="G21" s="2" t="inlineStr"/>
+      <c r="H21" s="2" t="inlineStr"/>
     </row>
     <row r="22">
-      <c r="A22" s="2" t="inlineStr">
+      <c r="A22" s="2" t="n">
+        <v>21</v>
+      </c>
+      <c r="B22" s="2" t="inlineStr">
         <is>
           <t>test_very_long_email_rejected</t>
         </is>
       </c>
-      <c r="B22" s="2" t="inlineStr">
+      <c r="C22" s="2" t="inlineStr">
+        <is>
+          <t>Negative / Security</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
         <is>
           <t>Extremely long email (500+ chars) is rejected by SSO</t>
         </is>
       </c>
-      <c r="C22" s="2" t="inlineStr">
-        <is>
-          <t>1. [UI] Verify text appears: Extremely long email (500+ chars) is rejected by SSO</t>
-        </is>
-      </c>
-      <c r="D22" s="2" t="inlineStr">
-        <is>
-          <t>No DB queries defined</t>
-        </is>
-      </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>Extremely long email (500+ chars) is rejected by SSO</t>
+          <t>User is NOT logged in; 500+ char email rejected by SSO</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr"/>
-      <c r="G22" s="2" t="inlineStr">
-        <is>
-          <t>UI</t>
-        </is>
-      </c>
+      <c r="G22" s="2" t="inlineStr"/>
+      <c r="H22" s="2" t="inlineStr"/>
     </row>
     <row r="23">
-      <c r="A23" s="2" t="inlineStr">
+      <c r="A23" s="2" t="n">
+        <v>22</v>
+      </c>
+      <c r="B23" s="2" t="inlineStr">
         <is>
           <t>test_special_characters_in_password</t>
         </is>
       </c>
-      <c r="B23" s="2" t="inlineStr">
+      <c r="C23" s="2" t="inlineStr">
+        <is>
+          <t>Negative / Security</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
         <is>
           <t>Wrong password with special characters shows proper error on SSO</t>
         </is>
       </c>
-      <c r="C23" s="2" t="inlineStr">
-        <is>
-          <t>1. [UI] Verify text appears: Wrong password with special characters shows proper error on SSO</t>
-        </is>
-      </c>
-      <c r="D23" s="2" t="inlineStr">
-        <is>
-          <t>No DB queries defined</t>
-        </is>
-      </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>Wrong password with special characters shows proper error on SSO</t>
+          <t>User is NOT logged in; wrong special-char password rejected</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr"/>
-      <c r="G23" s="2" t="inlineStr">
-        <is>
-          <t>UI</t>
-        </is>
-      </c>
+      <c r="G23" s="2" t="inlineStr"/>
+      <c r="H23" s="2" t="inlineStr"/>
     </row>
     <row r="24">
-      <c r="A24" s="2" t="inlineStr">
+      <c r="A24" s="2" t="n">
+        <v>23</v>
+      </c>
+      <c r="B24" s="2" t="inlineStr">
         <is>
           <t>test_remember_me_session_persists</t>
         </is>
       </c>
-      <c r="B24" s="2" t="inlineStr">
+      <c r="C24" s="2" t="inlineStr">
+        <is>
+          <t>Session / Post-Login</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
         <is>
           <t>Remember Me / Stay Signed In keeps session after browser restart simulation</t>
         </is>
       </c>
-      <c r="C24" s="2" t="inlineStr">
-        <is>
-          <t>1. [UI] Verify text appears: Remember Me / Stay Signed In keeps session after browser restart simulation</t>
-        </is>
-      </c>
-      <c r="D24" s="2" t="inlineStr">
-        <is>
-          <t>1. [verify_user_exists_and_active] (Variables: email)
-   SQL: SELECT is_active FROM auth_user WHERE email = '{email}' LIMIT 1
-   Expected: auth_user.is_active = 1 for the logged-in user
-2. [verify_last_login_updated] (Variables: email)
-   SQL: SELECT last_login FROM auth_user WHERE email = '{email}' LIMIT 1
-   Expected: auth_user.last_login is not null after successful login
-3. [verify_session_exists]
-   SQL: SELECT COUNT(*) FROM django_session WHERE expire_date &gt; NOW()
-   Expected: At least 1 active session exists in django_session</t>
-        </is>
-      </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>Remember Me / Stay Signed In keeps session after browser restart simulation</t>
+          <t>User is logged in after clicking Yes on 'Stay signed in?' prompt</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr"/>
-      <c r="G24" s="2" t="inlineStr">
-        <is>
-          <t>UI</t>
-        </is>
-      </c>
+      <c r="G24" s="2" t="inlineStr"/>
+      <c r="H24" s="2" t="inlineStr"/>
     </row>
     <row r="25">
-      <c r="A25" s="2" t="inlineStr">
+      <c r="A25" s="2" t="n">
+        <v>24</v>
+      </c>
+      <c r="B25" s="2" t="inlineStr">
         <is>
           <t>test_login_access_hcp_targeting_module</t>
         </is>
       </c>
-      <c r="B25" s="2" t="inlineStr">
+      <c r="C25" s="2" t="inlineStr">
+        <is>
+          <t>Session / Post-Login</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="inlineStr">
         <is>
           <t>After login, user can access HCP Targeting module and see specialties</t>
         </is>
       </c>
-      <c r="C25" s="2" t="inlineStr">
-        <is>
-          <t>1. [UI] Verify text appears: After login, user can access HCP Targeting module and see specialties</t>
-        </is>
-      </c>
-      <c r="D25" s="2" t="inlineStr">
-        <is>
-          <t>1. [verify_user_exists_and_active] (Variables: email)
-   SQL: SELECT is_active FROM auth_user WHERE email = '{email}' LIMIT 1
-   Expected: auth_user.is_active = 1 for the logged-in user
-2. [verify_last_login_updated] (Variables: email)
-   SQL: SELECT last_login FROM auth_user WHERE email = '{email}' LIMIT 1
-   Expected: auth_user.last_login is not null after successful login
-3. [verify_session_exists]
-   SQL: SELECT COUNT(*) FROM django_session WHERE expire_date &gt; NOW()
-   Expected: At least 1 active session exists in django_session</t>
-        </is>
-      </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>After login, user can access HCP Targeting module and see specialties</t>
+          <t>Dashboard loads with HCP/Specialty/Segmentation content visible</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr"/>
-      <c r="G25" s="2" t="inlineStr">
-        <is>
-          <t>UI</t>
-        </is>
-      </c>
+      <c r="G25" s="2" t="inlineStr"/>
+      <c r="H25" s="2" t="inlineStr"/>
     </row>
     <row r="26">
-      <c r="A26" s="2" t="inlineStr">
+      <c r="A26" s="2" t="n">
+        <v>25</v>
+      </c>
+      <c r="B26" s="2" t="inlineStr">
         <is>
           <t>test_mfa_prompt_appears_after_password</t>
         </is>
       </c>
-      <c r="B26" s="2" t="inlineStr">
+      <c r="C26" s="2" t="inlineStr">
+        <is>
+          <t>Session / Post-Login</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
         <is>
           <t>MFA (Authenticator app) prompt appears after valid email + password on SSO</t>
         </is>
       </c>
-      <c r="C26" s="2" t="inlineStr">
-        <is>
-          <t>1. [UI] Verify text appears: MFA (Authenticator app) prompt appears after valid email + password on SSO</t>
-        </is>
-      </c>
-      <c r="D26" s="2" t="inlineStr">
-        <is>
-          <t>No DB queries defined</t>
-        </is>
-      </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>MFA (Authenticator app) prompt appears after valid email + password on SSO</t>
+          <t>MFA prompt OR 'Stay signed in?' OR successful redirect appears</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr"/>
-      <c r="G26" s="2" t="inlineStr">
-        <is>
-          <t>UI</t>
-        </is>
-      </c>
+      <c r="G26" s="2" t="inlineStr"/>
+      <c r="H26" s="2" t="inlineStr"/>
     </row>
     <row r="27">
-      <c r="A27" s="2" t="inlineStr">
+      <c r="A27" s="2" t="n">
+        <v>26</v>
+      </c>
+      <c r="B27" s="2" t="inlineStr">
         <is>
           <t>test_session_expiry_redirects_to_login</t>
         </is>
       </c>
-      <c r="B27" s="2" t="inlineStr">
+      <c r="C27" s="2" t="inlineStr">
+        <is>
+          <t>Session / Post-Login</t>
+        </is>
+      </c>
+      <c r="D27" s="2" t="inlineStr">
         <is>
           <t>Accessing protected URL without session redirects to login page</t>
         </is>
       </c>
-      <c r="C27" s="2" t="inlineStr">
-        <is>
-          <t>1. [UI] Verify text appears: Accessing protected URL without session redirects to login page</t>
-        </is>
-      </c>
-      <c r="D27" s="2" t="inlineStr">
-        <is>
-          <t>1. [verify_user_exists_and_active] (Variables: email)
-   SQL: SELECT is_active FROM auth_user WHERE email = '{email}' LIMIT 1
-   Expected: auth_user.is_active = 1 for the logged-in user
-2. [verify_last_login_updated] (Variables: email)
-   SQL: SELECT last_login FROM auth_user WHERE email = '{email}' LIMIT 1
-   Expected: auth_user.last_login is not null after successful login
-3. [verify_session_exists]
-   SQL: SELECT COUNT(*) FROM django_session WHERE expire_date &gt; NOW()
-   Expected: At least 1 active session exists in django_session</t>
-        </is>
-      </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>Accessing protected URL without session redirects to login page</t>
+          <t>Unauthenticated access redirects to SSO or shows Sign In button</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr"/>
-      <c r="G27" s="2" t="inlineStr">
-        <is>
-          <t>UI</t>
-        </is>
-      </c>
+      <c r="G27" s="2" t="inlineStr"/>
+      <c r="H27" s="2" t="inlineStr"/>
     </row>
     <row r="28">
-      <c r="A28" s="2" t="inlineStr">
+      <c r="A28" s="2" t="n">
+        <v>27</v>
+      </c>
+      <c r="B28" s="2" t="inlineStr">
         <is>
           <t>test_logout_clears_session</t>
         </is>
       </c>
-      <c r="B28" s="2" t="inlineStr">
+      <c r="C28" s="2" t="inlineStr">
+        <is>
+          <t>Session / Post-Login</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
         <is>
           <t>After logout, navigating back to app redirects to login</t>
         </is>
       </c>
-      <c r="C28" s="2" t="inlineStr">
-        <is>
-          <t>1. [UI] Verify text appears: After logout, navigating back to app redirects to login</t>
-        </is>
-      </c>
-      <c r="D28" s="2" t="inlineStr">
-        <is>
-          <t>1. [verify_user_exists_and_active] (Variables: email)
-   SQL: SELECT is_active FROM auth_user WHERE email = '{email}' LIMIT 1
-   Expected: auth_user.is_active = 1 for the logged-in user
-2. [verify_last_login_updated] (Variables: email)
-   SQL: SELECT last_login FROM auth_user WHERE email = '{email}' LIMIT 1
-   Expected: auth_user.last_login is not null after successful login
-3. [verify_session_exists]
-   SQL: SELECT COUNT(*) FROM django_session WHERE expire_date &gt; NOW()
-   Expected: At least 1 active session exists in django_session</t>
-        </is>
-      </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>After logout, navigating back to app redirects to login</t>
+          <t>After logout, protected route redirects to SSO or /login</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr"/>
-      <c r="G28" s="2" t="inlineStr">
-        <is>
-          <t>UI</t>
-        </is>
-      </c>
+      <c r="G28" s="2" t="inlineStr"/>
+      <c r="H28" s="2" t="inlineStr"/>
     </row>
     <row r="29">
-      <c r="A29" s="2" t="inlineStr">
+      <c r="A29" s="2" t="n">
+        <v>28</v>
+      </c>
+      <c r="B29" s="2" t="inlineStr">
         <is>
           <t>test_account_lockout_after_multiple_failures</t>
         </is>
       </c>
-      <c r="B29" s="2" t="inlineStr">
+      <c r="C29" s="2" t="inlineStr">
+        <is>
+          <t>Session / Post-Login</t>
+        </is>
+      </c>
+      <c r="D29" s="2" t="inlineStr">
         <is>
           <t>Repeated wrong password attempts show lockout or throttling message</t>
         </is>
       </c>
-      <c r="C29" s="2" t="inlineStr">
-        <is>
-          <t>1. [UI] Verify text appears: Repeated wrong password attempts show lockout or throttling message</t>
-        </is>
-      </c>
-      <c r="D29" s="2" t="inlineStr">
-        <is>
-          <t>No DB queries defined</t>
-        </is>
-      </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>Repeated wrong password attempts show lockout or throttling message</t>
+          <t>User is NOT logged in after 3 wrong password attempts</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr"/>
-      <c r="G29" s="2" t="inlineStr">
-        <is>
-          <t>UI</t>
-        </is>
-      </c>
+      <c r="G29" s="2" t="inlineStr"/>
+      <c r="H29" s="2" t="inlineStr"/>
     </row>
     <row r="30">
-      <c r="A30" s="2" t="inlineStr">
+      <c r="A30" s="2" t="n">
+        <v>29</v>
+      </c>
+      <c r="B30" s="2" t="inlineStr">
         <is>
           <t>test_concurrent_session_same_browser</t>
         </is>
       </c>
-      <c r="B30" s="2" t="inlineStr">
+      <c r="C30" s="2" t="inlineStr">
+        <is>
+          <t>Session / Post-Login</t>
+        </is>
+      </c>
+      <c r="D30" s="2" t="inlineStr">
         <is>
           <t>Opening a second tab after login shows the app without re-authenticating</t>
         </is>
       </c>
-      <c r="C30" s="2" t="inlineStr">
-        <is>
-          <t>1. [UI] Verify text appears: Opening a second tab after login shows the app without re-authenticating</t>
-        </is>
-      </c>
-      <c r="D30" s="2" t="inlineStr">
-        <is>
-          <t>1. [verify_user_exists_and_active] (Variables: email)
-   SQL: SELECT is_active FROM auth_user WHERE email = '{email}' LIMIT 1
-   Expected: auth_user.is_active = 1 for the logged-in user
-2. [verify_last_login_updated] (Variables: email)
-   SQL: SELECT last_login FROM auth_user WHERE email = '{email}' LIMIT 1
-   Expected: auth_user.last_login is not null after successful login
-3. [verify_session_exists]
-   SQL: SELECT COUNT(*) FROM django_session WHERE expire_date &gt; NOW()
-   Expected: At least 1 active session exists in django_session</t>
-        </is>
-      </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>Opening a second tab after login shows the app without re-authenticating</t>
+          <t>Second tab lands on app or SSO, not an error page</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr"/>
-      <c r="G30" s="2" t="inlineStr">
-        <is>
-          <t>UI</t>
-        </is>
-      </c>
+      <c r="G30" s="2" t="inlineStr"/>
+      <c r="H30" s="2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
